--- a/mainWidget/mainWidget/src/database/壳体物性材料.xlsx
+++ b/mainWidget/mainWidget/src/database/壳体物性材料.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
@@ -10,16 +10,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>序号</t>
   </si>
@@ -72,159 +67,7 @@
     <t>40CrNiMoA</t>
   </si>
   <si>
-    <t>中碳合金结构钢</t>
-  </si>
-  <si>
-    <t>D406</t>
-  </si>
-  <si>
-    <t>超高强度结构钢</t>
-  </si>
-  <si>
-    <t>D406A</t>
-  </si>
-  <si>
-    <t>航空超高强度钢</t>
-  </si>
-  <si>
-    <t>30CrMnSiA</t>
-  </si>
-  <si>
-    <t>合金结构钢</t>
-  </si>
-  <si>
-    <r>
-      <t>TC4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ti-6Al-4V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）钛合金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>α+β</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>型钛合金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TC11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>钛合金</t>
-    </r>
-  </si>
-  <si>
-    <t>高温钛合金</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TA15 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>钛合金</t>
-    </r>
-  </si>
-  <si>
-    <t>高强钛合金</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TC21 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>钛合金</t>
-    </r>
-  </si>
-  <si>
-    <t>损伤容限钛合金</t>
-  </si>
-  <si>
     <t>ZL114A</t>
-  </si>
-  <si>
-    <t>铸造铝合金</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7075 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>铝合金</t>
-    </r>
-  </si>
-  <si>
-    <t>高强变形铝合金</t>
   </si>
   <si>
     <r>
@@ -244,51 +87,50 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>合金钢</t>
+  </si>
+  <si>
+    <t>7850</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
     <t>42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>41.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>41.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC4</t>
+  </si>
+  <si>
+    <t>钛合金</t>
+  </si>
+  <si>
+    <t>4430</t>
+  </si>
+  <si>
+    <t>520</t>
   </si>
   <si>
     <t>6.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铸铝</t>
+  </si>
+  <si>
+    <t>2700</t>
+  </si>
+  <si>
+    <t>963</t>
   </si>
   <si>
     <t>170</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +159,10 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -326,7 +172,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -362,35 +208,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -399,30 +222,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -683,7 +492,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -691,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.35546875" customWidth="1"/>
@@ -707,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -723,203 +532,63 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5">
-        <v>7850</v>
-      </c>
-      <c r="E2" s="5">
-        <v>470</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>26</v>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5">
-        <v>7850</v>
-      </c>
-      <c r="E3" s="5">
-        <v>465</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>27</v>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5">
-        <v>7850</v>
-      </c>
-      <c r="E4" s="5">
-        <v>468</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5">
-        <v>7850</v>
-      </c>
-      <c r="E5" s="5">
-        <v>460</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5">
-        <v>4430</v>
-      </c>
-      <c r="E6" s="5">
-        <v>520</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4450</v>
-      </c>
-      <c r="E7" s="5">
-        <v>515</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="5">
-        <v>4420</v>
-      </c>
-      <c r="E8" s="5">
-        <v>525</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="F4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D9" s="5">
-        <v>4440</v>
-      </c>
-      <c r="E9" s="5">
-        <v>518</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2700</v>
-      </c>
-      <c r="E10" s="5">
-        <v>963</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2810</v>
-      </c>
-      <c r="E11" s="5">
-        <v>920</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
